--- a/database/event/7435/event_7435_evp_summary.xlsx
+++ b/database/event/7435/event_7435_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>11.5821</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>6.3217</v>
       </c>
       <c r="D2" t="n">
         <v>4.2575</v>
@@ -545,7 +545,7 @@
         <v>7.3207</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3.9957</v>
       </c>
       <c r="D3" t="n">
         <v>2.536</v>
@@ -591,7 +591,7 @@
         <v>6.4233</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3.5059</v>
       </c>
       <c r="D4" t="n">
         <v>2.1735</v>
@@ -637,7 +637,7 @@
         <v>5.0816</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2.7736</v>
       </c>
       <c r="D5" t="n">
         <v>1.6315</v>
@@ -683,7 +683,7 @@
         <v>4.8185</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="D6" t="n">
         <v>1.5252</v>
@@ -729,7 +729,7 @@
         <v>4.43</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2.418</v>
       </c>
       <c r="D7" t="n">
         <v>1.3683</v>
@@ -775,7 +775,7 @@
         <v>4.4213</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2.4132</v>
       </c>
       <c r="D8" t="n">
         <v>1.3647</v>
@@ -821,7 +821,7 @@
         <v>4.3737</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.3872</v>
       </c>
       <c r="D9" t="n">
         <v>1.3455</v>
@@ -867,7 +867,7 @@
         <v>4.3581</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.3787</v>
       </c>
       <c r="D10" t="n">
         <v>1.3392</v>
@@ -913,7 +913,7 @@
         <v>3.9827</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2.1738</v>
       </c>
       <c r="D11" t="n">
         <v>1.1876</v>
@@ -959,7 +959,7 @@
         <v>3.7754</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2.0607</v>
       </c>
       <c r="D12" t="n">
         <v>1.1038</v>
@@ -1005,7 +1005,7 @@
         <v>3.7565</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2.0504</v>
       </c>
       <c r="D13" t="n">
         <v>1.0962</v>
@@ -1051,7 +1051,7 @@
         <v>3.6487</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.9915</v>
       </c>
       <c r="D14" t="n">
         <v>1.0526</v>
@@ -1097,7 +1097,7 @@
         <v>3.4746</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.8965</v>
       </c>
       <c r="D15" t="n">
         <v>0.9823</v>
@@ -1143,7 +1143,7 @@
         <v>3.4393</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.8772</v>
       </c>
       <c r="D16" t="n">
         <v>0.968</v>
@@ -1189,7 +1189,7 @@
         <v>3.4065</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.8593</v>
       </c>
       <c r="D17" t="n">
         <v>0.9548</v>
@@ -1235,7 +1235,7 @@
         <v>3.3634</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.8358</v>
       </c>
       <c r="D18" t="n">
         <v>0.9374</v>
@@ -1281,7 +1281,7 @@
         <v>3.0559</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.668</v>
       </c>
       <c r="D19" t="n">
         <v>0.8132</v>
@@ -1327,7 +1327,7 @@
         <v>3.0092</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.6425</v>
       </c>
       <c r="D20" t="n">
         <v>0.7943</v>
@@ -1373,7 +1373,7 @@
         <v>2.7375</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.4942</v>
       </c>
       <c r="D21" t="n">
         <v>0.6845</v>
@@ -1419,7 +1419,7 @@
         <v>2.6605</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.4521</v>
       </c>
       <c r="D22" t="n">
         <v>0.6534</v>
@@ -1465,7 +1465,7 @@
         <v>2.5244</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.3779</v>
       </c>
       <c r="D23" t="n">
         <v>0.5984</v>
@@ -1511,7 +1511,7 @@
         <v>2.3844</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.3014</v>
       </c>
       <c r="D24" t="n">
         <v>0.5419</v>
@@ -1557,7 +1557,7 @@
         <v>2.326</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.2696</v>
       </c>
       <c r="D25" t="n">
         <v>0.5183</v>
@@ -1603,7 +1603,7 @@
         <v>2.2482</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1.2271</v>
       </c>
       <c r="D26" t="n">
         <v>0.4869</v>
@@ -1649,7 +1649,7 @@
         <v>1.9247</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1.0505</v>
       </c>
       <c r="D27" t="n">
         <v>0.3562</v>
@@ -1695,7 +1695,7 @@
         <v>1.8253</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.9963</v>
       </c>
       <c r="D28" t="n">
         <v>0.316</v>
@@ -1741,7 +1741,7 @@
         <v>1.8237</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.9954</v>
       </c>
       <c r="D29" t="n">
         <v>0.3154</v>
@@ -1787,7 +1787,7 @@
         <v>1.5505</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="D30" t="n">
         <v>0.205</v>
@@ -1833,7 +1833,7 @@
         <v>1.4261</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.7784</v>
       </c>
       <c r="D31" t="n">
         <v>0.1548</v>
@@ -1879,7 +1879,7 @@
         <v>1.3775</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.7519</v>
       </c>
       <c r="D32" t="n">
         <v>0.1351</v>
@@ -1925,7 +1925,7 @@
         <v>1.3553</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.7397</v>
       </c>
       <c r="D33" t="n">
         <v>0.1261</v>
@@ -1971,7 +1971,7 @@
         <v>1.1391</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.6217</v>
       </c>
       <c r="D34" t="n">
         <v>0.0388</v>
@@ -2017,7 +2017,7 @@
         <v>1.0215</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.5576</v>
       </c>
       <c r="D35" t="n">
         <v>-0.008699999999999999</v>
@@ -2063,7 +2063,7 @@
         <v>1.0022</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.547</v>
       </c>
       <c r="D36" t="n">
         <v>-0.0165</v>
@@ -2109,7 +2109,7 @@
         <v>0.8255</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.4506</v>
       </c>
       <c r="D37" t="n">
         <v>-0.08790000000000001</v>
@@ -2155,7 +2155,7 @@
         <v>0.8022</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.4379</v>
       </c>
       <c r="D38" t="n">
         <v>-0.0973</v>
@@ -2201,7 +2201,7 @@
         <v>0.7441</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.4061</v>
       </c>
       <c r="D39" t="n">
         <v>-0.1208</v>
@@ -2247,7 +2247,7 @@
         <v>0.742</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.405</v>
       </c>
       <c r="D40" t="n">
         <v>-0.1216</v>
@@ -2293,7 +2293,7 @@
         <v>0.6865</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.3747</v>
       </c>
       <c r="D41" t="n">
         <v>-0.144</v>
@@ -2339,7 +2339,7 @@
         <v>0.6806</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.3715</v>
       </c>
       <c r="D42" t="n">
         <v>-0.1464</v>
@@ -2385,7 +2385,7 @@
         <v>0.6699000000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.3656</v>
       </c>
       <c r="D43" t="n">
         <v>-0.1507</v>
@@ -2431,7 +2431,7 @@
         <v>0.6393</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.3489</v>
       </c>
       <c r="D44" t="n">
         <v>-0.1631</v>
@@ -2477,7 +2477,7 @@
         <v>0.6373</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.3478</v>
       </c>
       <c r="D45" t="n">
         <v>-0.1639</v>
@@ -2523,7 +2523,7 @@
         <v>0.5599</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.3056</v>
       </c>
       <c r="D46" t="n">
         <v>-0.1952</v>
@@ -2569,7 +2569,7 @@
         <v>0.5526</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.3016</v>
       </c>
       <c r="D47" t="n">
         <v>-0.1981</v>
@@ -2615,7 +2615,7 @@
         <v>0.5042</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.2752</v>
       </c>
       <c r="D48" t="n">
         <v>-0.2177</v>
@@ -2661,7 +2661,7 @@
         <v>0.4677</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.2553</v>
       </c>
       <c r="D49" t="n">
         <v>-0.2324</v>
@@ -2707,7 +2707,7 @@
         <v>0.4299</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.2346</v>
       </c>
       <c r="D50" t="n">
         <v>-0.2477</v>
@@ -2753,7 +2753,7 @@
         <v>0.427</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.2331</v>
       </c>
       <c r="D51" t="n">
         <v>-0.2489</v>
@@ -2799,7 +2799,7 @@
         <v>0.2651</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>0.1447</v>
       </c>
       <c r="D52" t="n">
         <v>-0.3143</v>
@@ -2845,7 +2845,7 @@
         <v>0.1622</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>0.0885</v>
       </c>
       <c r="D53" t="n">
         <v>-0.3558</v>
@@ -2891,7 +2891,7 @@
         <v>0.1588</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>0.0867</v>
       </c>
       <c r="D54" t="n">
         <v>-0.3572</v>
@@ -2937,7 +2937,7 @@
         <v>0.0672</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>0.0367</v>
       </c>
       <c r="D55" t="n">
         <v>-0.3942</v>
@@ -2983,7 +2983,7 @@
         <v>0.0567</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>0.0309</v>
       </c>
       <c r="D56" t="n">
         <v>-0.3985</v>
@@ -3029,7 +3029,7 @@
         <v>0.0023</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>0.0013</v>
       </c>
       <c r="D57" t="n">
         <v>-0.4204</v>
@@ -3075,7 +3075,7 @@
         <v>-0.0527</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.0288</v>
       </c>
       <c r="D58" t="n">
         <v>-0.4427</v>
@@ -3121,7 +3121,7 @@
         <v>-0.2562</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.1398</v>
       </c>
       <c r="D59" t="n">
         <v>-0.5249</v>
@@ -3167,7 +3167,7 @@
         <v>-0.3372</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.184</v>
       </c>
       <c r="D60" t="n">
         <v>-0.5576</v>
@@ -3213,7 +3213,7 @@
         <v>-0.4241</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.2315</v>
       </c>
       <c r="D61" t="n">
         <v>-0.5927</v>
@@ -3259,7 +3259,7 @@
         <v>-0.4605</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.2513</v>
       </c>
       <c r="D62" t="n">
         <v>-0.6074000000000001</v>
@@ -3305,7 +3305,7 @@
         <v>-0.5534</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.3021</v>
       </c>
       <c r="D63" t="n">
         <v>-0.6449</v>
@@ -3351,7 +3351,7 @@
         <v>-0.5865</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.3201</v>
       </c>
       <c r="D64" t="n">
         <v>-0.6583</v>
@@ -3397,7 +3397,7 @@
         <v>-0.8202</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.4477</v>
       </c>
       <c r="D65" t="n">
         <v>-0.7527</v>
@@ -3443,7 +3443,7 @@
         <v>-0.8509</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.4644</v>
       </c>
       <c r="D66" t="n">
         <v>-0.7651</v>
@@ -3489,7 +3489,7 @@
         <v>-0.9671999999999999</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.5279</v>
       </c>
       <c r="D67" t="n">
         <v>-0.8121</v>
@@ -3535,7 +3535,7 @@
         <v>-1.0886</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.5942</v>
       </c>
       <c r="D68" t="n">
         <v>-0.8611</v>
@@ -3581,7 +3581,7 @@
         <v>-1.2143</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="D69" t="n">
         <v>-0.9119</v>
@@ -3627,7 +3627,7 @@
         <v>-1.3268</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.7242</v>
       </c>
       <c r="D70" t="n">
         <v>-0.9574</v>
@@ -3673,7 +3673,7 @@
         <v>-1.3394</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.7311</v>
       </c>
       <c r="D71" t="n">
         <v>-0.9625</v>
@@ -3719,7 +3719,7 @@
         <v>-1.4606</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.7972</v>
       </c>
       <c r="D72" t="n">
         <v>-1.0114</v>
@@ -3765,7 +3765,7 @@
         <v>-1.6703</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.9117</v>
       </c>
       <c r="D73" t="n">
         <v>-1.0961</v>
@@ -3811,7 +3811,7 @@
         <v>-1.6901</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.9225</v>
       </c>
       <c r="D74" t="n">
         <v>-1.1041</v>
@@ -3857,7 +3857,7 @@
         <v>-1.6957</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-0.9255</v>
       </c>
       <c r="D75" t="n">
         <v>-1.1064</v>
@@ -3903,7 +3903,7 @@
         <v>-1.9519</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-1.0654</v>
       </c>
       <c r="D76" t="n">
         <v>-1.2099</v>
@@ -3949,7 +3949,7 @@
         <v>-2.0946</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.1433</v>
       </c>
       <c r="D77" t="n">
         <v>-1.2675</v>
@@ -3995,7 +3995,7 @@
         <v>-2.4033</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.3118</v>
       </c>
       <c r="D78" t="n">
         <v>-1.3922</v>
@@ -4041,7 +4041,7 @@
         <v>-2.4839</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.3557</v>
       </c>
       <c r="D79" t="n">
         <v>-1.4248</v>
@@ -4087,7 +4087,7 @@
         <v>-3.9334</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-2.1469</v>
       </c>
       <c r="D80" t="n">
         <v>-2.0104</v>
@@ -4133,7 +4133,7 @@
         <v>-6.3095</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-3.4438</v>
       </c>
       <c r="D81" t="n">
         <v>-2.9703</v>

--- a/database/event/7435/event_7435_evp_summary.xlsx
+++ b/database/event/7435/event_7435_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>6.3217</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2575</v>
+        <v>4.1704</v>
       </c>
       <c r="E2" t="n">
         <v>11.5821</v>
@@ -548,7 +548,7 @@
         <v>3.9957</v>
       </c>
       <c r="D3" t="n">
-        <v>2.536</v>
+        <v>2.4727</v>
       </c>
       <c r="E3" t="n">
         <v>7.3207</v>
@@ -594,7 +594,7 @@
         <v>3.5059</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1735</v>
+        <v>2.1151</v>
       </c>
       <c r="E4" t="n">
         <v>6.4233</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.0816</v>
+        <v>5.058</v>
       </c>
       <c r="C5" t="n">
-        <v>2.7736</v>
+        <v>2.7607</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6315</v>
+        <v>1.5712</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0816</v>
+        <v>5.058</v>
       </c>
       <c r="F5" t="n">
-        <v>4.648</v>
+        <v>4.6244</v>
       </c>
       <c r="G5" t="n">
         <v>0.4336</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9851</v>
+        <v>4.9479</v>
       </c>
       <c r="I5" t="n">
         <v>5.0316</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.8185</v>
+        <v>4.7955</v>
       </c>
       <c r="C6" t="n">
-        <v>2.63</v>
+        <v>2.6175</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5252</v>
+        <v>1.4666</v>
       </c>
       <c r="E6" t="n">
-        <v>4.8185</v>
+        <v>4.7955</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0802</v>
+        <v>3.0573</v>
       </c>
       <c r="G6" t="n">
         <v>1.7382</v>
       </c>
       <c r="H6" t="n">
-        <v>3.0802</v>
+        <v>3.0573</v>
       </c>
       <c r="I6" t="n">
         <v>3.109</v>
@@ -732,7 +732,7 @@
         <v>2.418</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3683</v>
+        <v>1.321</v>
       </c>
       <c r="E7" t="n">
         <v>4.43</v>
@@ -778,7 +778,7 @@
         <v>2.4132</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3647</v>
+        <v>1.3175</v>
       </c>
       <c r="E8" t="n">
         <v>4.4213</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BOROS</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.3737</v>
+        <v>4.3581</v>
       </c>
       <c r="C9" t="n">
-        <v>2.3872</v>
+        <v>2.3787</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3455</v>
+        <v>1.2924</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3737</v>
+        <v>4.3581</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9446</v>
+        <v>2.6826</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4291</v>
+        <v>1.6755</v>
       </c>
       <c r="H9" t="n">
-        <v>2.9446</v>
+        <v>2.6826</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9721</v>
+        <v>2.1743</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4291</v>
+        <v>1.6755</v>
       </c>
       <c r="K9" t="n">
-        <v>212</v>
+        <v>136</v>
       </c>
       <c r="L9" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M9" t="n">
-        <v>4.4012</v>
+        <v>3.8498</v>
       </c>
       <c r="N9" t="n">
-        <v>313</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>BOROS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.3581</v>
+        <v>4.3518</v>
       </c>
       <c r="C10" t="n">
-        <v>2.3787</v>
+        <v>2.3753</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3392</v>
+        <v>1.2898</v>
       </c>
       <c r="E10" t="n">
-        <v>4.3581</v>
+        <v>4.3518</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6826</v>
+        <v>2.9227</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6755</v>
+        <v>1.4291</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6826</v>
+        <v>2.9227</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1743</v>
+        <v>2.9721</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6755</v>
+        <v>1.4291</v>
       </c>
       <c r="K10" t="n">
-        <v>136</v>
+        <v>212</v>
       </c>
       <c r="L10" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8498</v>
+        <v>4.4012</v>
       </c>
       <c r="N10" t="n">
-        <v>235</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.9827</v>
+        <v>3.9679</v>
       </c>
       <c r="C11" t="n">
-        <v>2.1738</v>
+        <v>2.1657</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1876</v>
+        <v>1.1369</v>
       </c>
       <c r="E11" t="n">
-        <v>3.9827</v>
+        <v>3.9679</v>
       </c>
       <c r="F11" t="n">
-        <v>3.9827</v>
+        <v>3.9679</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9827</v>
+        <v>3.9679</v>
       </c>
       <c r="I11" t="n">
         <v>4.0013</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>hades</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.7754</v>
+        <v>3.7565</v>
       </c>
       <c r="C12" t="n">
-        <v>2.0607</v>
+        <v>2.0504</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1038</v>
+        <v>1.0527</v>
       </c>
       <c r="E12" t="n">
-        <v>3.7754</v>
+        <v>3.7565</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2495</v>
+        <v>2.1166</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5259</v>
+        <v>1.6399</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2495</v>
+        <v>2.1166</v>
       </c>
       <c r="I12" t="n">
-        <v>3.2798</v>
+        <v>2.1166</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5259</v>
+        <v>1.6399</v>
       </c>
       <c r="K12" t="n">
-        <v>212</v>
+        <v>132</v>
       </c>
       <c r="L12" t="n">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8057</v>
+        <v>3.7565</v>
       </c>
       <c r="N12" t="n">
-        <v>313</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hades</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.7565</v>
+        <v>3.7512</v>
       </c>
       <c r="C13" t="n">
-        <v>2.0504</v>
+        <v>2.0475</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0962</v>
+        <v>1.0506</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7565</v>
+        <v>3.7512</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1166</v>
+        <v>3.2253</v>
       </c>
       <c r="G13" t="n">
-        <v>1.6399</v>
+        <v>0.5259</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1166</v>
+        <v>3.2253</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1166</v>
+        <v>3.2798</v>
       </c>
       <c r="J13" t="n">
-        <v>1.6399</v>
+        <v>0.5259</v>
       </c>
       <c r="K13" t="n">
-        <v>132</v>
+        <v>212</v>
       </c>
       <c r="L13" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7565</v>
+        <v>3.8057</v>
       </c>
       <c r="N13" t="n">
-        <v>196</v>
+        <v>313</v>
       </c>
     </row>
     <row r="14">
@@ -1054,7 +1054,7 @@
         <v>1.9915</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0526</v>
+        <v>1.0097</v>
       </c>
       <c r="E14" t="n">
         <v>3.6487</v>
@@ -1100,7 +1100,7 @@
         <v>1.8965</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9823</v>
+        <v>0.9404</v>
       </c>
       <c r="E15" t="n">
         <v>3.4746</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.4393</v>
+        <v>3.4184</v>
       </c>
       <c r="C16" t="n">
-        <v>1.8772</v>
+        <v>1.8658</v>
       </c>
       <c r="D16" t="n">
-        <v>0.968</v>
+        <v>0.918</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4393</v>
+        <v>3.4184</v>
       </c>
       <c r="F16" t="n">
-        <v>4.2802</v>
+        <v>4.2593</v>
       </c>
       <c r="G16" t="n">
         <v>-0.8409</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4083</v>
+        <v>4.3755</v>
       </c>
       <c r="I16" t="n">
         <v>4.4495</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.4065</v>
+        <v>3.3938</v>
       </c>
       <c r="C17" t="n">
-        <v>1.8593</v>
+        <v>1.8524</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9548</v>
+        <v>0.9082</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4065</v>
+        <v>3.3938</v>
       </c>
       <c r="F17" t="n">
-        <v>3.4065</v>
+        <v>3.3938</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.4065</v>
+        <v>3.3938</v>
       </c>
       <c r="I17" t="n">
         <v>3.4223</v>
@@ -1238,7 +1238,7 @@
         <v>1.8358</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9374</v>
+        <v>0.8961</v>
       </c>
       <c r="E18" t="n">
         <v>3.3634</v>
@@ -1284,7 +1284,7 @@
         <v>1.668</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8132</v>
+        <v>0.7736</v>
       </c>
       <c r="E19" t="n">
         <v>3.0559</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.0092</v>
+        <v>2.9979</v>
       </c>
       <c r="C20" t="n">
-        <v>1.6425</v>
+        <v>1.6363</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7943</v>
+        <v>0.7504999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>3.0092</v>
+        <v>2.9979</v>
       </c>
       <c r="F20" t="n">
-        <v>3.0092</v>
+        <v>2.9979</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3.0092</v>
+        <v>2.9979</v>
       </c>
       <c r="I20" t="n">
         <v>3.0232</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.7375</v>
+        <v>2.7272</v>
       </c>
       <c r="C21" t="n">
-        <v>1.4942</v>
+        <v>1.4885</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6845</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>2.7375</v>
+        <v>2.7272</v>
       </c>
       <c r="F21" t="n">
-        <v>2.7375</v>
+        <v>2.7272</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7375</v>
+        <v>2.7272</v>
       </c>
       <c r="I21" t="n">
         <v>2.7502</v>
@@ -1422,7 +1422,7 @@
         <v>1.4521</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6534</v>
+        <v>0.616</v>
       </c>
       <c r="E22" t="n">
         <v>2.6605</v>
@@ -1468,7 +1468,7 @@
         <v>1.3779</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5984</v>
+        <v>0.5618</v>
       </c>
       <c r="E23" t="n">
         <v>2.5244</v>
@@ -1514,7 +1514,7 @@
         <v>1.3014</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5419</v>
+        <v>0.506</v>
       </c>
       <c r="E24" t="n">
         <v>2.3844</v>
@@ -1560,7 +1560,7 @@
         <v>1.2696</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5183</v>
+        <v>0.4828</v>
       </c>
       <c r="E25" t="n">
         <v>2.326</v>
@@ -1606,7 +1606,7 @@
         <v>1.2271</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4869</v>
+        <v>0.4518</v>
       </c>
       <c r="E26" t="n">
         <v>2.2482</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.9247</v>
+        <v>1.9154</v>
       </c>
       <c r="C27" t="n">
-        <v>1.0505</v>
+        <v>1.0455</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3562</v>
+        <v>0.3192</v>
       </c>
       <c r="E27" t="n">
-        <v>1.9247</v>
+        <v>1.9154</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2478</v>
+        <v>1.2385</v>
       </c>
       <c r="G27" t="n">
         <v>0.6768999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>1.2478</v>
+        <v>1.2385</v>
       </c>
       <c r="I27" t="n">
         <v>1.2594</v>
@@ -1698,7 +1698,7 @@
         <v>0.9963</v>
       </c>
       <c r="D28" t="n">
-        <v>0.316</v>
+        <v>0.2833</v>
       </c>
       <c r="E28" t="n">
         <v>1.8253</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.8237</v>
+        <v>1.8169</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9954</v>
+        <v>0.9917</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3154</v>
+        <v>0.2799</v>
       </c>
       <c r="E29" t="n">
-        <v>1.8237</v>
+        <v>1.8169</v>
       </c>
       <c r="F29" t="n">
-        <v>1.8237</v>
+        <v>1.8169</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.8237</v>
+        <v>1.8169</v>
       </c>
       <c r="I29" t="n">
         <v>1.8322</v>
@@ -1790,7 +1790,7 @@
         <v>0.8463000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>0.205</v>
+        <v>0.1738</v>
       </c>
       <c r="E30" t="n">
         <v>1.5505</v>
@@ -1836,7 +1836,7 @@
         <v>0.7784</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1548</v>
+        <v>0.1242</v>
       </c>
       <c r="E31" t="n">
         <v>1.4261</v>
@@ -1882,7 +1882,7 @@
         <v>0.7519</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1351</v>
+        <v>0.1049</v>
       </c>
       <c r="E32" t="n">
         <v>1.3775</v>
@@ -1928,7 +1928,7 @@
         <v>0.7397</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1261</v>
+        <v>0.096</v>
       </c>
       <c r="E33" t="n">
         <v>1.3553</v>
@@ -1974,7 +1974,7 @@
         <v>0.6217</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0388</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="E34" t="n">
         <v>1.1391</v>
@@ -2020,7 +2020,7 @@
         <v>0.5576</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0369</v>
       </c>
       <c r="E35" t="n">
         <v>1.0215</v>
@@ -2066,7 +2066,7 @@
         <v>0.547</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0165</v>
+        <v>-0.0446</v>
       </c>
       <c r="E36" t="n">
         <v>1.0022</v>
@@ -2112,7 +2112,7 @@
         <v>0.4506</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.115</v>
       </c>
       <c r="E37" t="n">
         <v>0.8255</v>
@@ -2158,7 +2158,7 @@
         <v>0.4379</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0973</v>
+        <v>-0.1243</v>
       </c>
       <c r="E38" t="n">
         <v>0.8022</v>
@@ -2204,7 +2204,7 @@
         <v>0.4061</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1208</v>
+        <v>-0.1475</v>
       </c>
       <c r="E39" t="n">
         <v>0.7441</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.742</v>
+        <v>0.7392</v>
       </c>
       <c r="C40" t="n">
-        <v>0.405</v>
+        <v>0.4035</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1216</v>
+        <v>-0.1494</v>
       </c>
       <c r="E40" t="n">
-        <v>0.742</v>
+        <v>0.7392</v>
       </c>
       <c r="F40" t="n">
-        <v>0.742</v>
+        <v>0.7392</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.742</v>
+        <v>0.7392</v>
       </c>
       <c r="I40" t="n">
         <v>0.7454</v>
@@ -2296,7 +2296,7 @@
         <v>0.3747</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.144</v>
+        <v>-0.1704</v>
       </c>
       <c r="E41" t="n">
         <v>0.6865</v>
@@ -2342,7 +2342,7 @@
         <v>0.3715</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1464</v>
+        <v>-0.1728</v>
       </c>
       <c r="E42" t="n">
         <v>0.6806</v>
@@ -2388,7 +2388,7 @@
         <v>0.3656</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1507</v>
+        <v>-0.177</v>
       </c>
       <c r="E43" t="n">
         <v>0.6699000000000001</v>
@@ -2434,7 +2434,7 @@
         <v>0.3489</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1631</v>
+        <v>-0.1892</v>
       </c>
       <c r="E44" t="n">
         <v>0.6393</v>
@@ -2480,7 +2480,7 @@
         <v>0.3478</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1639</v>
+        <v>-0.19</v>
       </c>
       <c r="E45" t="n">
         <v>0.6373</v>
@@ -2526,7 +2526,7 @@
         <v>0.3056</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1952</v>
+        <v>-0.2208</v>
       </c>
       <c r="E46" t="n">
         <v>0.5599</v>
@@ -2572,7 +2572,7 @@
         <v>0.3016</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1981</v>
+        <v>-0.2238</v>
       </c>
       <c r="E47" t="n">
         <v>0.5526</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5042</v>
+        <v>0.5007</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2752</v>
+        <v>0.2733</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2177</v>
+        <v>-0.2444</v>
       </c>
       <c r="E48" t="n">
-        <v>0.5042</v>
+        <v>0.5007</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4642</v>
+        <v>0.4607</v>
       </c>
       <c r="G48" t="n">
         <v>0.04</v>
       </c>
       <c r="H48" t="n">
-        <v>0.4642</v>
+        <v>0.4607</v>
       </c>
       <c r="I48" t="n">
         <v>0.4685</v>
@@ -2664,7 +2664,7 @@
         <v>0.2553</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2324</v>
+        <v>-0.2576</v>
       </c>
       <c r="E49" t="n">
         <v>0.4677</v>
@@ -2710,7 +2710,7 @@
         <v>0.2346</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.2477</v>
+        <v>-0.2726</v>
       </c>
       <c r="E50" t="n">
         <v>0.4299</v>
@@ -2756,7 +2756,7 @@
         <v>0.2331</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.2489</v>
+        <v>-0.2738</v>
       </c>
       <c r="E51" t="n">
         <v>0.427</v>
@@ -2802,7 +2802,7 @@
         <v>0.1447</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3143</v>
+        <v>-0.3383</v>
       </c>
       <c r="E52" t="n">
         <v>0.2651</v>
@@ -2848,7 +2848,7 @@
         <v>0.0885</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3558</v>
+        <v>-0.3793</v>
       </c>
       <c r="E53" t="n">
         <v>0.1622</v>
@@ -2894,7 +2894,7 @@
         <v>0.0867</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.3572</v>
+        <v>-0.3806</v>
       </c>
       <c r="E54" t="n">
         <v>0.1588</v>
@@ -2940,7 +2940,7 @@
         <v>0.0367</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.3942</v>
+        <v>-0.4171</v>
       </c>
       <c r="E55" t="n">
         <v>0.0672</v>
@@ -2986,7 +2986,7 @@
         <v>0.0309</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.3985</v>
+        <v>-0.4213</v>
       </c>
       <c r="E56" t="n">
         <v>0.0567</v>
@@ -3032,7 +3032,7 @@
         <v>0.0013</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4204</v>
+        <v>-0.443</v>
       </c>
       <c r="E57" t="n">
         <v>0.0023</v>
@@ -3078,7 +3078,7 @@
         <v>-0.0288</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4427</v>
+        <v>-0.4649</v>
       </c>
       <c r="E58" t="n">
         <v>-0.0527</v>
@@ -3124,7 +3124,7 @@
         <v>-0.1398</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5249</v>
+        <v>-0.546</v>
       </c>
       <c r="E59" t="n">
         <v>-0.2562</v>
@@ -3170,7 +3170,7 @@
         <v>-0.184</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5576</v>
+        <v>-0.5783</v>
       </c>
       <c r="E60" t="n">
         <v>-0.3372</v>
@@ -3216,7 +3216,7 @@
         <v>-0.2315</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5927</v>
+        <v>-0.6129</v>
       </c>
       <c r="E61" t="n">
         <v>-0.4241</v>
@@ -3262,7 +3262,7 @@
         <v>-0.2513</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.6274</v>
       </c>
       <c r="E62" t="n">
         <v>-0.4605</v>
@@ -3308,7 +3308,7 @@
         <v>-0.3021</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6449</v>
+        <v>-0.6644</v>
       </c>
       <c r="E63" t="n">
         <v>-0.5534</v>
@@ -3354,7 +3354,7 @@
         <v>-0.3201</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6583</v>
+        <v>-0.6776</v>
       </c>
       <c r="E64" t="n">
         <v>-0.5865</v>
@@ -3400,7 +3400,7 @@
         <v>-0.4477</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7527</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="E65" t="n">
         <v>-0.8202</v>
@@ -3446,7 +3446,7 @@
         <v>-0.4644</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7651</v>
+        <v>-0.7829</v>
       </c>
       <c r="E66" t="n">
         <v>-0.8509</v>
@@ -3492,7 +3492,7 @@
         <v>-0.5279</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8121</v>
+        <v>-0.8292</v>
       </c>
       <c r="E67" t="n">
         <v>-0.9671999999999999</v>
@@ -3532,25 +3532,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.0886</v>
+        <v>-1.0846</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5942</v>
+        <v>-0.592</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8611</v>
+        <v>-0.876</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.0886</v>
+        <v>-1.0846</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.0886</v>
+        <v>-1.0846</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.0886</v>
+        <v>-1.0846</v>
       </c>
       <c r="I68" t="n">
         <v>-1.0937</v>
@@ -3584,7 +3584,7 @@
         <v>-0.6627999999999999</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9119</v>
+        <v>-0.9277</v>
       </c>
       <c r="E69" t="n">
         <v>-1.2143</v>
@@ -3630,7 +3630,7 @@
         <v>-0.7242</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9574</v>
+        <v>-0.9725</v>
       </c>
       <c r="E70" t="n">
         <v>-1.3268</v>
@@ -3670,25 +3670,25 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.3394</v>
+        <v>-1.3369</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.7311</v>
+        <v>-0.7297</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9625</v>
+        <v>-0.9765</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.3394</v>
+        <v>-1.3369</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.3394</v>
+        <v>-0.3369</v>
       </c>
       <c r="G71" t="n">
         <v>-1</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.3394</v>
+        <v>-0.3369</v>
       </c>
       <c r="I71" t="n">
         <v>-0.3426</v>
@@ -3722,7 +3722,7 @@
         <v>-0.7972</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0114</v>
+        <v>-1.0258</v>
       </c>
       <c r="E72" t="n">
         <v>-1.4606</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.6703</v>
+        <v>-1.6641</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.9117</v>
+        <v>-0.9083</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0961</v>
+        <v>-1.1069</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.6703</v>
+        <v>-1.6641</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.6703</v>
+        <v>-1.6641</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.6703</v>
+        <v>-1.6641</v>
       </c>
       <c r="I73" t="n">
         <v>-1.6781</v>
@@ -3814,7 +3814,7 @@
         <v>-0.9225</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1041</v>
+        <v>-1.1172</v>
       </c>
       <c r="E74" t="n">
         <v>-1.6901</v>
@@ -3860,7 +3860,7 @@
         <v>-0.9255</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1064</v>
+        <v>-1.1195</v>
       </c>
       <c r="E75" t="n">
         <v>-1.6957</v>
@@ -3900,25 +3900,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.9519</v>
+        <v>-1.9446</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.0654</v>
+        <v>-1.0614</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2099</v>
+        <v>-1.2186</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.9519</v>
+        <v>-1.9446</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.9519</v>
+        <v>-1.9446</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.9519</v>
+        <v>-1.9446</v>
       </c>
       <c r="I76" t="n">
         <v>-1.961</v>
@@ -3952,7 +3952,7 @@
         <v>-1.1433</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2675</v>
+        <v>-1.2784</v>
       </c>
       <c r="E77" t="n">
         <v>-2.0946</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.4033</v>
+        <v>-2.3831</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.3118</v>
+        <v>-1.3007</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3922</v>
+        <v>-1.3933</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.4033</v>
+        <v>-2.3831</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.7121</v>
+        <v>-2.6919</v>
       </c>
       <c r="G78" t="n">
         <v>0.3088</v>
       </c>
       <c r="H78" t="n">
-        <v>-2.7121</v>
+        <v>-2.6919</v>
       </c>
       <c r="I78" t="n">
         <v>-2.7374</v>
@@ -4044,7 +4044,7 @@
         <v>-1.3557</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.4248</v>
+        <v>-1.4335</v>
       </c>
       <c r="E79" t="n">
         <v>-2.4839</v>
@@ -4090,7 +4090,7 @@
         <v>-2.1469</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.0104</v>
+        <v>-2.011</v>
       </c>
       <c r="E80" t="n">
         <v>-3.9334</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-6.3095</v>
+        <v>-6.2774</v>
       </c>
       <c r="C81" t="n">
-        <v>-3.4438</v>
+        <v>-3.4263</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.9703</v>
+        <v>-2.9448</v>
       </c>
       <c r="E81" t="n">
-        <v>-6.3095</v>
+        <v>-6.2774</v>
       </c>
       <c r="F81" t="n">
-        <v>-4.3095</v>
+        <v>-4.2774</v>
       </c>
       <c r="G81" t="n">
         <v>-2</v>
       </c>
       <c r="H81" t="n">
-        <v>-4.3095</v>
+        <v>-4.2774</v>
       </c>
       <c r="I81" t="n">
         <v>-4.3497</v>

--- a/database/event/7435/event_7435_evp_summary.xlsx
+++ b/database/event/7435/event_7435_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.6786</v>
+        <v>12.3486</v>
       </c>
       <c r="C2" t="n">
-        <v>6.3744</v>
+        <v>6.7401</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6921</v>
+        <v>4.902</v>
       </c>
       <c r="E2" t="n">
-        <v>11.6786</v>
+        <v>12.3486</v>
       </c>
       <c r="F2" t="n">
         <v>4.5807</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.8788</v>
+        <v>7.1335</v>
       </c>
       <c r="C3" t="n">
-        <v>3.7546</v>
+        <v>3.8936</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5072</v>
+        <v>2.5726</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8788</v>
+        <v>7.1335</v>
       </c>
       <c r="F3" t="n">
         <v>3.8432</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.0424</v>
+        <v>6.1009</v>
       </c>
       <c r="C4" t="n">
-        <v>3.298</v>
+        <v>3.33</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1264</v>
+        <v>2.1113</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0424</v>
+        <v>6.1009</v>
       </c>
       <c r="F4" t="n">
         <v>3.4577</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.2</v>
+        <v>5.6195</v>
       </c>
       <c r="C5" t="n">
-        <v>2.8382</v>
+        <v>3.0672</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7429</v>
+        <v>1.8963</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2</v>
+        <v>5.6195</v>
       </c>
       <c r="F5" t="n">
         <v>4.7723</v>
@@ -676,47 +676,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5455</v>
+        <v>4.553</v>
       </c>
       <c r="C6" t="n">
-        <v>2.481</v>
+        <v>2.4851</v>
       </c>
       <c r="D6" t="n">
-        <v>1.445</v>
+        <v>1.4199</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5455</v>
+        <v>4.553</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8988</v>
+        <v>2.7222</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6467</v>
+        <v>1.662</v>
       </c>
       <c r="H6" t="n">
-        <v>4.6699</v>
+        <v>3.2331</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5217</v>
+        <v>3.4019</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6467</v>
+        <v>1.662</v>
       </c>
       <c r="K6" t="n">
-        <v>136</v>
+        <v>212</v>
       </c>
       <c r="L6" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1684</v>
+        <v>5.0639</v>
       </c>
       <c r="N6" t="n">
-        <v>235</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7">
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.4205</v>
+        <v>4.5363</v>
       </c>
       <c r="C7" t="n">
-        <v>2.4128</v>
+        <v>2.476</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3881</v>
+        <v>1.4124</v>
       </c>
       <c r="E7" t="n">
-        <v>4.4205</v>
+        <v>4.5363</v>
       </c>
       <c r="F7" t="n">
         <v>2.3087</v>
@@ -768,139 +768,139 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.3842</v>
+        <v>4.4283</v>
       </c>
       <c r="C8" t="n">
-        <v>2.393</v>
+        <v>2.417</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3716</v>
+        <v>1.3642</v>
       </c>
       <c r="E8" t="n">
-        <v>4.3842</v>
+        <v>4.4283</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7222</v>
+        <v>2.8988</v>
       </c>
       <c r="G8" t="n">
-        <v>1.662</v>
+        <v>1.6467</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2331</v>
+        <v>4.6699</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4019</v>
+        <v>2.5217</v>
       </c>
       <c r="J8" t="n">
-        <v>1.662</v>
+        <v>1.6467</v>
       </c>
       <c r="K8" t="n">
-        <v>212</v>
+        <v>136</v>
       </c>
       <c r="L8" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M8" t="n">
-        <v>5.0639</v>
+        <v>4.1684</v>
       </c>
       <c r="N8" t="n">
-        <v>313</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BOROS</t>
+          <t>hades</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.108</v>
+        <v>4.3007</v>
       </c>
       <c r="C9" t="n">
-        <v>2.2422</v>
+        <v>2.3474</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2458</v>
+        <v>1.3072</v>
       </c>
       <c r="E9" t="n">
-        <v>4.108</v>
+        <v>4.3007</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8746</v>
+        <v>2.5652</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2334</v>
+        <v>1.415</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5666</v>
+        <v>2.8894</v>
       </c>
       <c r="I9" t="n">
-        <v>3.7528</v>
+        <v>2.8894</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2334</v>
+        <v>1.415</v>
       </c>
       <c r="K9" t="n">
-        <v>212</v>
+        <v>132</v>
       </c>
       <c r="L9" t="n">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="M9" t="n">
-        <v>4.9862</v>
+        <v>4.3044</v>
       </c>
       <c r="N9" t="n">
-        <v>313</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>hades</t>
+          <t>BOROS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.9802</v>
+        <v>4.299</v>
       </c>
       <c r="C10" t="n">
-        <v>2.1725</v>
+        <v>2.3465</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1877</v>
+        <v>1.3064</v>
       </c>
       <c r="E10" t="n">
-        <v>3.9802</v>
+        <v>4.299</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5652</v>
+        <v>2.8746</v>
       </c>
       <c r="G10" t="n">
-        <v>1.415</v>
+        <v>1.2334</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8894</v>
+        <v>3.5666</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8894</v>
+        <v>3.7528</v>
       </c>
       <c r="J10" t="n">
-        <v>1.415</v>
+        <v>1.2334</v>
       </c>
       <c r="K10" t="n">
-        <v>132</v>
+        <v>212</v>
       </c>
       <c r="L10" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="M10" t="n">
-        <v>4.3044</v>
+        <v>4.9862</v>
       </c>
       <c r="N10" t="n">
-        <v>196</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.9631</v>
+        <v>4.1991</v>
       </c>
       <c r="C11" t="n">
-        <v>2.1631</v>
+        <v>2.2919</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1799</v>
+        <v>1.2618</v>
       </c>
       <c r="E11" t="n">
-        <v>3.9631</v>
+        <v>4.1991</v>
       </c>
       <c r="F11" t="n">
         <v>3.6546</v>
@@ -952,139 +952,139 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.7102</v>
+        <v>3.9138</v>
       </c>
       <c r="C12" t="n">
-        <v>2.0251</v>
+        <v>2.1362</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0648</v>
+        <v>1.1344</v>
       </c>
       <c r="E12" t="n">
-        <v>3.7102</v>
+        <v>3.9138</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6101</v>
+        <v>3.6593</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1001</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6101</v>
+        <v>5.284</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6101</v>
+        <v>5.4202</v>
       </c>
       <c r="J12" t="n">
-        <v>2.1001</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>160</v>
+        <v>234</v>
       </c>
       <c r="L12" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7102</v>
+        <v>5.4202</v>
       </c>
       <c r="N12" t="n">
-        <v>303</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.6593</v>
+        <v>3.7225</v>
       </c>
       <c r="C13" t="n">
-        <v>1.9973</v>
+        <v>2.0318</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0416</v>
+        <v>1.0489</v>
       </c>
       <c r="E13" t="n">
-        <v>3.6593</v>
+        <v>3.7225</v>
       </c>
       <c r="F13" t="n">
-        <v>3.6593</v>
+        <v>2.5147</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.142</v>
       </c>
       <c r="H13" t="n">
-        <v>5.284</v>
+        <v>3.4028</v>
       </c>
       <c r="I13" t="n">
-        <v>5.4202</v>
+        <v>1.8375</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1.142</v>
       </c>
       <c r="K13" t="n">
-        <v>234</v>
+        <v>167</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M13" t="n">
-        <v>5.4202</v>
+        <v>2.9795</v>
       </c>
       <c r="N13" t="n">
-        <v>234</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.6567</v>
+        <v>3.7065</v>
       </c>
       <c r="C14" t="n">
-        <v>1.9959</v>
+        <v>2.0231</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0404</v>
+        <v>1.0418</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6567</v>
+        <v>3.7065</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5147</v>
+        <v>1.6101</v>
       </c>
       <c r="G14" t="n">
-        <v>1.142</v>
+        <v>2.1001</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4028</v>
+        <v>1.6101</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8375</v>
+        <v>1.6101</v>
       </c>
       <c r="J14" t="n">
-        <v>1.142</v>
+        <v>2.1001</v>
       </c>
       <c r="K14" t="n">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="L14" t="n">
-        <v>40</v>
+        <v>143</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9795</v>
+        <v>3.7102</v>
       </c>
       <c r="N14" t="n">
-        <v>207</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15">
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.4895</v>
+        <v>3.6439</v>
       </c>
       <c r="C15" t="n">
-        <v>1.9046</v>
+        <v>1.9889</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9643</v>
+        <v>1.0138</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4895</v>
+        <v>3.6439</v>
       </c>
       <c r="F15" t="n">
         <v>4.0605</v>
@@ -1136,35 +1136,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.4368</v>
+        <v>3.4057</v>
       </c>
       <c r="C16" t="n">
-        <v>1.8759</v>
+        <v>1.8589</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9403</v>
+        <v>0.9074</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4368</v>
+        <v>3.4057</v>
       </c>
       <c r="F16" t="n">
-        <v>4.4368</v>
+        <v>3.8009</v>
       </c>
       <c r="G16" t="n">
-        <v>-1</v>
+        <v>-0.6244</v>
       </c>
       <c r="H16" t="n">
-        <v>9.7446</v>
+        <v>7.6464</v>
       </c>
       <c r="I16" t="n">
-        <v>5.262</v>
+        <v>4.129</v>
       </c>
       <c r="J16" t="n">
-        <v>-1</v>
+        <v>-0.6244</v>
       </c>
       <c r="K16" t="n">
         <v>167</v>
@@ -1173,7 +1173,7 @@
         <v>40</v>
       </c>
       <c r="M16" t="n">
-        <v>4.262</v>
+        <v>3.504599999999999</v>
       </c>
       <c r="N16" t="n">
         <v>207</v>
@@ -1182,47 +1182,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.4362</v>
+        <v>3.3878</v>
       </c>
       <c r="C17" t="n">
-        <v>1.8755</v>
+        <v>1.8491</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8994</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4362</v>
+        <v>3.3878</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2732</v>
+        <v>4.4368</v>
       </c>
       <c r="G17" t="n">
-        <v>1.163</v>
+        <v>-1</v>
       </c>
       <c r="H17" t="n">
-        <v>2.606</v>
+        <v>9.7446</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4072</v>
+        <v>5.262</v>
       </c>
       <c r="J17" t="n">
-        <v>1.163</v>
+        <v>-1</v>
       </c>
       <c r="K17" t="n">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="L17" t="n">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="M17" t="n">
-        <v>2.5702</v>
+        <v>4.262</v>
       </c>
       <c r="N17" t="n">
-        <v>235</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18">
@@ -1232,16 +1232,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.2946</v>
+        <v>3.2705</v>
       </c>
       <c r="C18" t="n">
-        <v>1.7982</v>
+        <v>1.7851</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8756</v>
+        <v>0.847</v>
       </c>
       <c r="E18" t="n">
-        <v>3.2946</v>
+        <v>3.2705</v>
       </c>
       <c r="F18" t="n">
         <v>2.666</v>
@@ -1274,47 +1274,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.1765</v>
+        <v>3.2151</v>
       </c>
       <c r="C19" t="n">
-        <v>1.7338</v>
+        <v>1.7548</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8218</v>
+        <v>0.8223</v>
       </c>
       <c r="E19" t="n">
-        <v>3.1765</v>
+        <v>3.2151</v>
       </c>
       <c r="F19" t="n">
-        <v>3.8009</v>
+        <v>2.2732</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6244</v>
+        <v>1.163</v>
       </c>
       <c r="H19" t="n">
-        <v>7.6464</v>
+        <v>2.606</v>
       </c>
       <c r="I19" t="n">
-        <v>4.129</v>
+        <v>1.4072</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6244</v>
+        <v>1.163</v>
       </c>
       <c r="K19" t="n">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="L19" t="n">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="M19" t="n">
-        <v>3.504599999999999</v>
+        <v>2.5702</v>
       </c>
       <c r="N19" t="n">
-        <v>207</v>
+        <v>235</v>
       </c>
     </row>
     <row r="20">
@@ -1324,16 +1324,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.9641</v>
+        <v>3.0174</v>
       </c>
       <c r="C20" t="n">
-        <v>1.6179</v>
+        <v>1.6469</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7251</v>
+        <v>0.734</v>
       </c>
       <c r="E20" t="n">
-        <v>2.9641</v>
+        <v>3.0174</v>
       </c>
       <c r="F20" t="n">
         <v>1.1408</v>
@@ -1366,32 +1366,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.9384</v>
+        <v>2.8943</v>
       </c>
       <c r="C21" t="n">
-        <v>1.6038</v>
+        <v>1.5798</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7134</v>
+        <v>0.679</v>
       </c>
       <c r="E21" t="n">
-        <v>2.9384</v>
+        <v>2.8943</v>
       </c>
       <c r="F21" t="n">
-        <v>2.9384</v>
+        <v>2.7046</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.7063</v>
+        <v>3.1946</v>
       </c>
       <c r="I21" t="n">
-        <v>3.8018</v>
+        <v>3.2769</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.8018</v>
+        <v>3.2769</v>
       </c>
       <c r="N21" t="n">
         <v>259</v>
@@ -1412,93 +1412,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.7412</v>
+        <v>2.884</v>
       </c>
       <c r="C22" t="n">
-        <v>1.4962</v>
+        <v>1.5741</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6236</v>
+        <v>0.6744</v>
       </c>
       <c r="E22" t="n">
-        <v>2.7412</v>
+        <v>2.884</v>
       </c>
       <c r="F22" t="n">
-        <v>2.7412</v>
+        <v>2.9384</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3.2746</v>
+        <v>3.7063</v>
       </c>
       <c r="I22" t="n">
-        <v>3.359</v>
+        <v>3.8018</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.359</v>
+        <v>3.8018</v>
       </c>
       <c r="N22" t="n">
-        <v>234</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.7046</v>
+        <v>2.877</v>
       </c>
       <c r="C23" t="n">
-        <v>1.4762</v>
+        <v>1.5703</v>
       </c>
       <c r="D23" t="n">
-        <v>0.607</v>
+        <v>0.6713</v>
       </c>
       <c r="E23" t="n">
-        <v>2.7046</v>
+        <v>2.877</v>
       </c>
       <c r="F23" t="n">
-        <v>2.7046</v>
+        <v>2.7412</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3.1946</v>
+        <v>3.2746</v>
       </c>
       <c r="I23" t="n">
-        <v>3.2769</v>
+        <v>3.359</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>259</v>
+        <v>234</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2769</v>
+        <v>3.359</v>
       </c>
       <c r="N23" t="n">
-        <v>259</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.6679</v>
+        <v>2.8524</v>
       </c>
       <c r="C24" t="n">
-        <v>1.4562</v>
+        <v>1.5569</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5903</v>
+        <v>0.6603</v>
       </c>
       <c r="E24" t="n">
-        <v>2.6679</v>
+        <v>2.8524</v>
       </c>
       <c r="F24" t="n">
         <v>2.6679</v>
@@ -1550,507 +1550,507 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>nawwk</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.5627</v>
+        <v>2.7134</v>
       </c>
       <c r="C25" t="n">
-        <v>1.3988</v>
+        <v>1.481</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5424</v>
+        <v>0.5982</v>
       </c>
       <c r="E25" t="n">
-        <v>2.5627</v>
+        <v>2.7134</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7432</v>
+        <v>2.4228</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8195</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7432</v>
+        <v>2.5779</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8342</v>
+        <v>2.5779</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8195</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>212</v>
+        <v>115</v>
       </c>
       <c r="L25" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.6537</v>
+        <v>2.5779</v>
       </c>
       <c r="N25" t="n">
-        <v>313</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.4666</v>
+        <v>2.5385</v>
       </c>
       <c r="C26" t="n">
-        <v>1.3463</v>
+        <v>1.3856</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4986</v>
+        <v>0.5201</v>
       </c>
       <c r="E26" t="n">
-        <v>2.4666</v>
+        <v>2.5385</v>
       </c>
       <c r="F26" t="n">
-        <v>2.4666</v>
+        <v>2.4091</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.6737</v>
+        <v>2.5478</v>
       </c>
       <c r="I26" t="n">
-        <v>2.6737</v>
+        <v>2.5478</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.6737</v>
+        <v>2.5478</v>
       </c>
       <c r="N26" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nawwk</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.4228</v>
+        <v>2.5372</v>
       </c>
       <c r="C27" t="n">
-        <v>1.3224</v>
+        <v>1.3848</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4787</v>
+        <v>0.5195</v>
       </c>
       <c r="E27" t="n">
-        <v>2.4228</v>
+        <v>2.5372</v>
       </c>
       <c r="F27" t="n">
-        <v>2.4228</v>
+        <v>1.7432</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.8195</v>
       </c>
       <c r="H27" t="n">
-        <v>2.5779</v>
+        <v>1.7432</v>
       </c>
       <c r="I27" t="n">
-        <v>2.5779</v>
+        <v>1.8342</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.8195</v>
       </c>
       <c r="K27" t="n">
-        <v>115</v>
+        <v>212</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M27" t="n">
-        <v>2.5779</v>
+        <v>2.6537</v>
       </c>
       <c r="N27" t="n">
-        <v>115</v>
+        <v>313</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.4091</v>
+        <v>2.4807</v>
       </c>
       <c r="C28" t="n">
-        <v>1.3149</v>
+        <v>1.354</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4725</v>
+        <v>0.4943</v>
       </c>
       <c r="E28" t="n">
-        <v>2.4091</v>
+        <v>2.4807</v>
       </c>
       <c r="F28" t="n">
-        <v>2.4091</v>
+        <v>2.4666</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.5478</v>
+        <v>2.6737</v>
       </c>
       <c r="I28" t="n">
-        <v>2.5478</v>
+        <v>2.6737</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.5478</v>
+        <v>2.6737</v>
       </c>
       <c r="N28" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.3866</v>
+        <v>2.308</v>
       </c>
       <c r="C29" t="n">
-        <v>1.3026</v>
+        <v>1.2597</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4622</v>
+        <v>0.4171</v>
       </c>
       <c r="E29" t="n">
-        <v>2.3866</v>
+        <v>2.308</v>
       </c>
       <c r="F29" t="n">
-        <v>2.3866</v>
+        <v>2.0762</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.4986</v>
+        <v>2.0762</v>
       </c>
       <c r="I29" t="n">
-        <v>2.563</v>
+        <v>2.0762</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>259</v>
+        <v>143</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.563</v>
+        <v>2.0762</v>
       </c>
       <c r="N29" t="n">
-        <v>259</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.0762</v>
+        <v>2.288</v>
       </c>
       <c r="C30" t="n">
-        <v>1.1332</v>
+        <v>1.2488</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3209</v>
+        <v>0.4082</v>
       </c>
       <c r="E30" t="n">
-        <v>2.0762</v>
+        <v>2.288</v>
       </c>
       <c r="F30" t="n">
-        <v>2.0762</v>
+        <v>2.3866</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2.0762</v>
+        <v>2.4986</v>
       </c>
       <c r="I30" t="n">
-        <v>2.0762</v>
+        <v>2.563</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>143</v>
+        <v>259</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.0762</v>
+        <v>2.563</v>
       </c>
       <c r="N30" t="n">
-        <v>143</v>
+        <v>259</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>Goofy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.8531</v>
+        <v>1.9014</v>
       </c>
       <c r="C31" t="n">
-        <v>1.0114</v>
+        <v>1.0378</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2194</v>
+        <v>0.2355</v>
       </c>
       <c r="E31" t="n">
-        <v>1.8531</v>
+        <v>1.9014</v>
       </c>
       <c r="F31" t="n">
-        <v>2.6689</v>
+        <v>1.3548</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.8158</v>
+        <v>0.4953</v>
       </c>
       <c r="H31" t="n">
-        <v>3.9115</v>
+        <v>1.3548</v>
       </c>
       <c r="I31" t="n">
-        <v>2.1122</v>
+        <v>1.3548</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.8158</v>
+        <v>0.4953</v>
       </c>
       <c r="K31" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L31" t="n">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="M31" t="n">
-        <v>1.2964</v>
+        <v>1.8501</v>
       </c>
       <c r="N31" t="n">
-        <v>235</v>
+        <v>196</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Goofy</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.8501</v>
+        <v>1.8211</v>
       </c>
       <c r="C32" t="n">
-        <v>1.0098</v>
+        <v>0.994</v>
       </c>
       <c r="D32" t="n">
-        <v>0.218</v>
+        <v>0.1996</v>
       </c>
       <c r="E32" t="n">
-        <v>1.8501</v>
+        <v>1.8211</v>
       </c>
       <c r="F32" t="n">
-        <v>1.3548</v>
+        <v>1.8374</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4953</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.3548</v>
+        <v>1.8374</v>
       </c>
       <c r="I32" t="n">
-        <v>1.3548</v>
+        <v>1.8374</v>
       </c>
       <c r="J32" t="n">
-        <v>0.4953</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="L32" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.8501</v>
+        <v>1.8374</v>
       </c>
       <c r="N32" t="n">
-        <v>196</v>
+        <v>144</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.8374</v>
+        <v>1.7847</v>
       </c>
       <c r="C33" t="n">
-        <v>1.0029</v>
+        <v>0.9741</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2122</v>
+        <v>0.1834</v>
       </c>
       <c r="E33" t="n">
-        <v>1.8374</v>
+        <v>1.7847</v>
       </c>
       <c r="F33" t="n">
-        <v>1.8374</v>
+        <v>1.7215</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.8374</v>
+        <v>1.7215</v>
       </c>
       <c r="I33" t="n">
-        <v>1.8374</v>
+        <v>1.7215</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.8374</v>
+        <v>1.7215</v>
       </c>
       <c r="N33" t="n">
-        <v>144</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>DemQQ</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.7215</v>
+        <v>1.5851</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9396</v>
+        <v>0.8652</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1595</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>1.7215</v>
+        <v>1.5851</v>
       </c>
       <c r="F34" t="n">
-        <v>1.7215</v>
+        <v>1.4105</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.7215</v>
+        <v>1.4105</v>
       </c>
       <c r="I34" t="n">
-        <v>1.7215</v>
+        <v>1.4105</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.7215</v>
+        <v>1.4105</v>
       </c>
       <c r="N34" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.5223</v>
+        <v>1.5671</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8309</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0688</v>
+        <v>0.0862</v>
       </c>
       <c r="E35" t="n">
-        <v>1.5223</v>
+        <v>1.5671</v>
       </c>
       <c r="F35" t="n">
-        <v>2.3624</v>
+        <v>2.6689</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.8401</v>
+        <v>-0.8158</v>
       </c>
       <c r="H35" t="n">
-        <v>2.9002</v>
+        <v>3.9115</v>
       </c>
       <c r="I35" t="n">
-        <v>1.5661</v>
+        <v>2.1122</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.8401</v>
+        <v>-0.8158</v>
       </c>
       <c r="K35" t="n">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="L35" t="n">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7260000000000001</v>
+        <v>1.2964</v>
       </c>
       <c r="N35" t="n">
-        <v>207</v>
+        <v>235</v>
       </c>
     </row>
     <row r="36">
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.4199</v>
+        <v>1.4544</v>
       </c>
       <c r="C36" t="n">
-        <v>0.775</v>
+        <v>0.7938</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0222</v>
+        <v>0.0358</v>
       </c>
       <c r="E36" t="n">
-        <v>1.4199</v>
+        <v>1.4544</v>
       </c>
       <c r="F36" t="n">
         <v>0.8919</v>
@@ -2102,354 +2102,354 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DemQQ</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.4105</v>
+        <v>1.384</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7699</v>
+        <v>0.7554</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0179</v>
+        <v>0.0044</v>
       </c>
       <c r="E37" t="n">
-        <v>1.4105</v>
+        <v>1.384</v>
       </c>
       <c r="F37" t="n">
-        <v>1.4105</v>
+        <v>2.3624</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.8401</v>
       </c>
       <c r="H37" t="n">
-        <v>1.4105</v>
+        <v>2.9002</v>
       </c>
       <c r="I37" t="n">
-        <v>1.4105</v>
+        <v>1.5661</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.8401</v>
       </c>
       <c r="K37" t="n">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M37" t="n">
-        <v>1.4105</v>
+        <v>0.7260000000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>144</v>
+        <v>207</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>flayy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.2832</v>
+        <v>1.3564</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7004</v>
+        <v>0.7403</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0401</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>1.2832</v>
+        <v>1.3564</v>
       </c>
       <c r="F38" t="n">
-        <v>1.2832</v>
+        <v>1.1149</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.2832</v>
+        <v>1.1149</v>
       </c>
       <c r="I38" t="n">
-        <v>1.2832</v>
+        <v>1.1149</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>181</v>
+        <v>109</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.2832</v>
+        <v>1.1149</v>
       </c>
       <c r="N38" t="n">
-        <v>181</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>Woro2k</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.2376</v>
+        <v>1.3013</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6755</v>
+        <v>0.7103</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0608</v>
+        <v>-0.0326</v>
       </c>
       <c r="E39" t="n">
-        <v>1.2376</v>
+        <v>1.3013</v>
       </c>
       <c r="F39" t="n">
-        <v>1.2376</v>
+        <v>1.1245</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.2376</v>
+        <v>1.1245</v>
       </c>
       <c r="I39" t="n">
-        <v>1.2695</v>
+        <v>1.1245</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>234</v>
+        <v>144</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1.2695</v>
+        <v>1.1245</v>
       </c>
       <c r="N39" t="n">
-        <v>234</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.1393</v>
+        <v>1.2869</v>
       </c>
       <c r="C40" t="n">
-        <v>0.6218</v>
+        <v>0.7024</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1056</v>
+        <v>-0.039</v>
       </c>
       <c r="E40" t="n">
-        <v>1.1393</v>
+        <v>1.2869</v>
       </c>
       <c r="F40" t="n">
-        <v>1.1393</v>
+        <v>1.2832</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.1393</v>
+        <v>1.2832</v>
       </c>
       <c r="I40" t="n">
-        <v>1.1393</v>
+        <v>1.2832</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>140</v>
+        <v>181</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.1393</v>
+        <v>1.2832</v>
       </c>
       <c r="N40" t="n">
-        <v>140</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Woro2k</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.1245</v>
+        <v>1.2635</v>
       </c>
       <c r="C41" t="n">
-        <v>0.6138</v>
+        <v>0.6896</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1123</v>
+        <v>-0.0494</v>
       </c>
       <c r="E41" t="n">
-        <v>1.1245</v>
+        <v>1.2635</v>
       </c>
       <c r="F41" t="n">
-        <v>1.1245</v>
+        <v>1.1393</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.1245</v>
+        <v>1.1393</v>
       </c>
       <c r="I41" t="n">
-        <v>1.1245</v>
+        <v>1.1393</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.1245</v>
+        <v>1.1393</v>
       </c>
       <c r="N41" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.1209</v>
+        <v>1.2627</v>
       </c>
       <c r="C42" t="n">
-        <v>0.6118</v>
+        <v>0.6892</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1139</v>
+        <v>-0.0498</v>
       </c>
       <c r="E42" t="n">
-        <v>1.1209</v>
+        <v>1.2627</v>
       </c>
       <c r="F42" t="n">
-        <v>1.1209</v>
+        <v>1.2376</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.1209</v>
+        <v>1.2376</v>
       </c>
       <c r="I42" t="n">
-        <v>1.1209</v>
+        <v>1.2695</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>144</v>
+        <v>234</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.1209</v>
+        <v>1.2695</v>
       </c>
       <c r="N42" t="n">
-        <v>144</v>
+        <v>234</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>flayy</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.1149</v>
+        <v>1.2525</v>
       </c>
       <c r="C43" t="n">
-        <v>0.6085</v>
+        <v>0.6836</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1167</v>
+        <v>-0.0544</v>
       </c>
       <c r="E43" t="n">
-        <v>1.1149</v>
+        <v>1.2525</v>
       </c>
       <c r="F43" t="n">
-        <v>1.1149</v>
+        <v>1.0659</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.1149</v>
+        <v>1.0659</v>
       </c>
       <c r="I43" t="n">
-        <v>1.1149</v>
+        <v>1.0659</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1.1149</v>
+        <v>1.0659</v>
       </c>
       <c r="N43" t="n">
-        <v>109</v>
+        <v>144</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.0659</v>
+        <v>1.1799</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5818</v>
+        <v>0.644</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.139</v>
+        <v>-0.0868</v>
       </c>
       <c r="E44" t="n">
-        <v>1.0659</v>
+        <v>1.1799</v>
       </c>
       <c r="F44" t="n">
-        <v>1.0659</v>
+        <v>1.1209</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.0659</v>
+        <v>1.1209</v>
       </c>
       <c r="I44" t="n">
-        <v>1.0659</v>
+        <v>1.1209</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1.0659</v>
+        <v>1.1209</v>
       </c>
       <c r="N44" t="n">
         <v>144</v>
@@ -2470,185 +2470,185 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.0534</v>
+        <v>1.1395</v>
       </c>
       <c r="C45" t="n">
-        <v>0.575</v>
+        <v>0.622</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1447</v>
+        <v>-0.1048</v>
       </c>
       <c r="E45" t="n">
-        <v>1.0534</v>
+        <v>1.1395</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9692</v>
+        <v>0.9597</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0842</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9692</v>
+        <v>0.9597</v>
       </c>
       <c r="I45" t="n">
-        <v>1.0198</v>
+        <v>0.9597</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0842</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>218</v>
+        <v>115</v>
       </c>
       <c r="L45" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1.104</v>
+        <v>0.9597</v>
       </c>
       <c r="N45" t="n">
-        <v>259</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.9713000000000001</v>
+        <v>1.0258</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5302</v>
+        <v>0.5599</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.182</v>
+        <v>-0.1556</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9713000000000001</v>
+        <v>1.0258</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.8488</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.8488</v>
       </c>
       <c r="I46" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.8488</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.8488</v>
       </c>
       <c r="N46" t="n">
-        <v>143</v>
+        <v>132</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.9597</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5238</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1873</v>
+        <v>-0.1836</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9597</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9597</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9597</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9597</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.9597</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>115</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8488</v>
+        <v>0.9022</v>
       </c>
       <c r="C48" t="n">
-        <v>0.4633</v>
+        <v>0.4924</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2378</v>
+        <v>-0.2108</v>
       </c>
       <c r="E48" t="n">
-        <v>0.8488</v>
+        <v>0.9022</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8488</v>
+        <v>0.9692</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>0.0842</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8488</v>
+        <v>0.9692</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8488</v>
+        <v>1.0198</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>0.0842</v>
       </c>
       <c r="K48" t="n">
-        <v>132</v>
+        <v>218</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M48" t="n">
-        <v>0.8488</v>
+        <v>1.104</v>
       </c>
       <c r="N48" t="n">
-        <v>132</v>
+        <v>259</v>
       </c>
     </row>
     <row r="49">
@@ -2658,16 +2658,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.802</v>
+        <v>0.678</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4377</v>
+        <v>0.3701</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2591</v>
+        <v>-0.311</v>
       </c>
       <c r="E49" t="n">
-        <v>0.802</v>
+        <v>0.678</v>
       </c>
       <c r="F49" t="n">
         <v>0.802</v>
@@ -2704,16 +2704,16 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6443</v>
+        <v>0.6392</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3517</v>
+        <v>0.3489</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3309</v>
+        <v>-0.3283</v>
       </c>
       <c r="E50" t="n">
-        <v>0.6443</v>
+        <v>0.6392</v>
       </c>
       <c r="F50" t="n">
         <v>0.6443</v>
@@ -2746,216 +2746,216 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>olimp</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5989</v>
+        <v>0.5996</v>
       </c>
       <c r="C51" t="n">
-        <v>0.3269</v>
+        <v>0.3273</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3516</v>
+        <v>-0.346</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5989</v>
+        <v>0.5996</v>
       </c>
       <c r="F51" t="n">
-        <v>0.5989</v>
+        <v>0.524</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.5989</v>
+        <v>0.524</v>
       </c>
       <c r="I51" t="n">
-        <v>0.5989</v>
+        <v>0.524</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.5989</v>
+        <v>0.524</v>
       </c>
       <c r="N51" t="n">
-        <v>109</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5849</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3192</v>
+        <v>0.2891</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3579</v>
+        <v>-0.3772</v>
       </c>
       <c r="E52" t="n">
-        <v>0.5849</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="F52" t="n">
-        <v>0.5849</v>
+        <v>0.5523</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.5849</v>
+        <v>0.5523</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5849</v>
+        <v>0.5665</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>143</v>
+        <v>234</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.5849</v>
+        <v>0.5665</v>
       </c>
       <c r="N52" t="n">
-        <v>143</v>
+        <v>234</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>olimp</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5523</v>
+        <v>0.4992</v>
       </c>
       <c r="C53" t="n">
-        <v>0.3015</v>
+        <v>0.2725</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3728</v>
+        <v>-0.3908</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5523</v>
+        <v>0.4992</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5523</v>
+        <v>0.5989</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.5523</v>
+        <v>0.5989</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5665</v>
+        <v>0.5989</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>234</v>
+        <v>109</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.5665</v>
+        <v>0.5989</v>
       </c>
       <c r="N53" t="n">
-        <v>234</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.524</v>
+        <v>0.459</v>
       </c>
       <c r="C54" t="n">
-        <v>0.286</v>
+        <v>0.2505</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.3857</v>
+        <v>-0.4088</v>
       </c>
       <c r="E54" t="n">
-        <v>0.524</v>
+        <v>0.459</v>
       </c>
       <c r="F54" t="n">
-        <v>0.524</v>
+        <v>0.2679</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.524</v>
+        <v>0.2679</v>
       </c>
       <c r="I54" t="n">
-        <v>0.524</v>
+        <v>0.2679</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.524</v>
+        <v>0.2679</v>
       </c>
       <c r="N54" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4283</v>
+        <v>0.4553</v>
       </c>
       <c r="C55" t="n">
-        <v>0.2338</v>
+        <v>0.2485</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4292</v>
+        <v>-0.4104</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4283</v>
+        <v>0.4553</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4283</v>
+        <v>0.38</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.4283</v>
+        <v>0.38</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4283</v>
+        <v>0.38</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.4283</v>
+        <v>0.38</v>
       </c>
       <c r="N55" t="n">
         <v>132</v>
@@ -2976,185 +2976,185 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4012</v>
+        <v>0.4211</v>
       </c>
       <c r="C56" t="n">
-        <v>0.219</v>
+        <v>0.2298</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4416</v>
+        <v>-0.4257</v>
       </c>
       <c r="E56" t="n">
-        <v>0.4012</v>
+        <v>0.4211</v>
       </c>
       <c r="F56" t="n">
-        <v>0.4012</v>
+        <v>0.5849</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.4012</v>
+        <v>0.5849</v>
       </c>
       <c r="I56" t="n">
-        <v>0.4115</v>
+        <v>0.5849</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>259</v>
+        <v>143</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.4115</v>
+        <v>0.5849</v>
       </c>
       <c r="N56" t="n">
-        <v>259</v>
+        <v>143</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.397</v>
+        <v>0.3651</v>
       </c>
       <c r="C57" t="n">
-        <v>0.2167</v>
+        <v>0.1993</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4435</v>
+        <v>-0.4507</v>
       </c>
       <c r="E57" t="n">
-        <v>0.397</v>
+        <v>0.3651</v>
       </c>
       <c r="F57" t="n">
-        <v>0.397</v>
+        <v>0.4012</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.397</v>
+        <v>0.4012</v>
       </c>
       <c r="I57" t="n">
-        <v>0.397</v>
+        <v>0.4115</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>181</v>
+        <v>259</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.397</v>
+        <v>0.4115</v>
       </c>
       <c r="N57" t="n">
-        <v>181</v>
+        <v>259</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.38</v>
+        <v>0.3052</v>
       </c>
       <c r="C58" t="n">
-        <v>0.2074</v>
+        <v>0.1666</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4512</v>
+        <v>-0.4775</v>
       </c>
       <c r="E58" t="n">
-        <v>0.38</v>
+        <v>0.3052</v>
       </c>
       <c r="F58" t="n">
-        <v>0.38</v>
+        <v>0.397</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.38</v>
+        <v>0.397</v>
       </c>
       <c r="I58" t="n">
-        <v>0.38</v>
+        <v>0.397</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.38</v>
+        <v>0.397</v>
       </c>
       <c r="N58" t="n">
-        <v>132</v>
+        <v>181</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.2679</v>
+        <v>0.2137</v>
       </c>
       <c r="C59" t="n">
-        <v>0.1462</v>
+        <v>0.1166</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5022</v>
+        <v>-0.5184</v>
       </c>
       <c r="E59" t="n">
-        <v>0.2679</v>
+        <v>0.2137</v>
       </c>
       <c r="F59" t="n">
-        <v>0.2679</v>
+        <v>0.4283</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2679</v>
+        <v>0.4283</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2679</v>
+        <v>0.4283</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.2679</v>
+        <v>0.4283</v>
       </c>
       <c r="N59" t="n">
-        <v>143</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60">
@@ -3164,16 +3164,16 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.185</v>
+        <v>0.016</v>
       </c>
       <c r="C60" t="n">
-        <v>0.101</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.54</v>
+        <v>-0.6067</v>
       </c>
       <c r="E60" t="n">
-        <v>0.185</v>
+        <v>0.016</v>
       </c>
       <c r="F60" t="n">
         <v>0.185</v>
@@ -3210,16 +3210,16 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.0401</v>
+        <v>-0.1927</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0219</v>
+        <v>-0.1052</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6059</v>
+        <v>-0.6999</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0401</v>
+        <v>-0.1927</v>
       </c>
       <c r="F61" t="n">
         <v>0.0401</v>
@@ -3252,93 +3252,93 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.2612</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.0414</v>
+        <v>-0.1426</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6587</v>
+        <v>-0.7305</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.2612</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.3124</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.3124</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.3124</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>140</v>
+        <v>181</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.3124</v>
       </c>
       <c r="N62" t="n">
-        <v>140</v>
+        <v>181</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.1374</v>
+        <v>-0.3318</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.075</v>
+        <v>-0.1811</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6868</v>
+        <v>-0.762</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.1374</v>
+        <v>-0.3318</v>
       </c>
       <c r="F63" t="n">
-        <v>0.8626</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.8626</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8626</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="J63" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="L63" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.1374</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="N63" t="n">
-        <v>196</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64">
@@ -3348,16 +3348,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.2495</v>
+        <v>-0.3878</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.1362</v>
+        <v>-0.2117</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7378</v>
+        <v>-0.787</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.2495</v>
+        <v>-0.3878</v>
       </c>
       <c r="F64" t="n">
         <v>-0.2495</v>
@@ -3390,415 +3390,415 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>sNx</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.2564</v>
+        <v>-0.4045</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.1399</v>
+        <v>-0.2208</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7409</v>
+        <v>-0.7945</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.2564</v>
+        <v>-0.4045</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.2564</v>
+        <v>0.8626</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.2564</v>
+        <v>0.8626</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2564</v>
+        <v>0.8626</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K65" t="n">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.2564</v>
+        <v>-0.1374</v>
       </c>
       <c r="N65" t="n">
-        <v>109</v>
+        <v>196</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>dycha</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.2611</v>
+        <v>-0.4986</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.1425</v>
+        <v>-0.2721</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7431</v>
+        <v>-0.8365</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.2611</v>
+        <v>-0.4986</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4879</v>
+        <v>0.1364</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.749</v>
+        <v>-0.6609</v>
       </c>
       <c r="H66" t="n">
-        <v>0.4879</v>
+        <v>0.1364</v>
       </c>
       <c r="I66" t="n">
-        <v>0.5134</v>
+        <v>0.1364</v>
       </c>
       <c r="J66" t="n">
-        <v>-0.749</v>
+        <v>-0.6609</v>
       </c>
       <c r="K66" t="n">
-        <v>218</v>
+        <v>132</v>
       </c>
       <c r="L66" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.2356</v>
+        <v>-0.5245000000000001</v>
       </c>
       <c r="N66" t="n">
-        <v>259</v>
+        <v>196</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>sNx</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.3124</v>
+        <v>-0.5248</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.1705</v>
+        <v>-0.2864</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7664</v>
+        <v>-0.8482</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.3124</v>
+        <v>-0.5248</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.3124</v>
+        <v>-0.2564</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.3124</v>
+        <v>-0.2564</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.3124</v>
+        <v>-0.2564</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>181</v>
+        <v>109</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.3124</v>
+        <v>-0.2564</v>
       </c>
       <c r="N67" t="n">
-        <v>181</v>
+        <v>109</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.4387</v>
+        <v>-0.5954</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2394</v>
+        <v>-0.325</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8239</v>
+        <v>-0.8798</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.4387</v>
+        <v>-0.5954</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.4387</v>
+        <v>-0.4667</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.4387</v>
+        <v>-0.4667</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.45</v>
+        <v>-0.4667</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>234</v>
+        <v>140</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.45</v>
+        <v>-0.4667</v>
       </c>
       <c r="N68" t="n">
-        <v>234</v>
+        <v>140</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.4667</v>
+        <v>-0.6293</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.2547</v>
+        <v>-0.3435</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8367</v>
+        <v>-0.8949</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.4667</v>
+        <v>-0.6293</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.4667</v>
+        <v>0.4879</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>-0.749</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.4667</v>
+        <v>0.4879</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4667</v>
+        <v>0.5134</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>-0.749</v>
       </c>
       <c r="K69" t="n">
-        <v>140</v>
+        <v>218</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.4667</v>
+        <v>-0.2356</v>
       </c>
       <c r="N69" t="n">
-        <v>140</v>
+        <v>259</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>dycha</t>
+          <t>kRaSnaL</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.5245</v>
+        <v>-0.7985</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.2863</v>
+        <v>-0.4358</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.863</v>
+        <v>-0.9705</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.5245</v>
+        <v>-0.7985</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1364</v>
+        <v>-0.699</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.6609</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>0.1364</v>
+        <v>-0.699</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1364</v>
+        <v>-0.699</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.6609</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="L70" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.5245000000000001</v>
+        <v>-0.699</v>
       </c>
       <c r="N70" t="n">
-        <v>196</v>
+        <v>144</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kRaSnaL</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.699</v>
+        <v>-0.847</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.3815</v>
+        <v>-0.4623</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9424</v>
+        <v>-0.9922</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.699</v>
+        <v>-0.847</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.699</v>
+        <v>-0.4387</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.699</v>
+        <v>-0.4387</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.699</v>
+        <v>-0.45</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>144</v>
+        <v>234</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.699</v>
+        <v>-0.45</v>
       </c>
       <c r="N71" t="n">
-        <v>144</v>
+        <v>234</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Keoz</t>
+          <t>nicoodoz</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.963</v>
+        <v>-1.043</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.5256</v>
+        <v>-0.5693</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0626</v>
+        <v>-1.0797</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.963</v>
+        <v>-1.043</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.963</v>
+        <v>-1.1132</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.963</v>
+        <v>-1.1132</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.963</v>
+        <v>-1.1419</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>144</v>
+        <v>259</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.963</v>
+        <v>-1.1419</v>
       </c>
       <c r="N72" t="n">
-        <v>144</v>
+        <v>259</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>nicoodoz</t>
+          <t>Keoz</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.1132</v>
+        <v>-1.1195</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.6076</v>
+        <v>-0.611</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.131</v>
+        <v>-1.1139</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.1132</v>
+        <v>-1.1195</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.1132</v>
+        <v>-0.963</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.1132</v>
+        <v>-0.963</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.1419</v>
+        <v>-0.963</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>259</v>
+        <v>144</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.1419</v>
+        <v>-0.963</v>
       </c>
       <c r="N73" t="n">
-        <v>259</v>
+        <v>144</v>
       </c>
     </row>
     <row r="74">
@@ -3808,16 +3808,16 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.1244</v>
+        <v>-1.4326</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.6137</v>
+        <v>-0.7819</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1361</v>
+        <v>-1.2537</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.1244</v>
+        <v>-1.4326</v>
       </c>
       <c r="F74" t="n">
         <v>-1.1244</v>
@@ -3850,93 +3850,93 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CacaNito</t>
+          <t>kisserek</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.2906</v>
+        <v>-1.5353</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.7044</v>
+        <v>-0.838</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.2117</v>
+        <v>-1.2996</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.2906</v>
+        <v>-1.5353</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.2906</v>
+        <v>-1.3503</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.2906</v>
+        <v>-1.3503</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.2906</v>
+        <v>-1.3503</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.2906</v>
+        <v>-1.3503</v>
       </c>
       <c r="N75" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kisserek</t>
+          <t>CacaNito</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.3503</v>
+        <v>-1.5745</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.737</v>
+        <v>-0.8594000000000001</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2389</v>
+        <v>-1.3171</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.3503</v>
+        <v>-1.5745</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.3503</v>
+        <v>-1.2906</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.3503</v>
+        <v>-1.2906</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.3503</v>
+        <v>-1.2906</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.3503</v>
+        <v>-1.2906</v>
       </c>
       <c r="N76" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="77">
@@ -3946,16 +3946,16 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.6471</v>
+        <v>-1.8734</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.899</v>
+        <v>-1.0225</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.374</v>
+        <v>-1.4506</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.6471</v>
+        <v>-1.8734</v>
       </c>
       <c r="F77" t="n">
         <v>-1.9345</v>
@@ -3992,16 +3992,16 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.947</v>
+        <v>-2.0232</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.0627</v>
+        <v>-1.1043</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.5105</v>
+        <v>-1.5175</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.947</v>
+        <v>-2.0232</v>
       </c>
       <c r="F78" t="n">
         <v>-1.947</v>
@@ -4038,16 +4038,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.0821</v>
+        <v>-2.2508</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.1364</v>
+        <v>-1.2285</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.572</v>
+        <v>-1.6192</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.0821</v>
+        <v>-2.2508</v>
       </c>
       <c r="F79" t="n">
         <v>-2.0821</v>
@@ -4084,16 +4084,16 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.6725</v>
+        <v>-2.9691</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.4587</v>
+        <v>-1.6206</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.8408</v>
+        <v>-1.9401</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.6725</v>
+        <v>-2.9691</v>
       </c>
       <c r="F80" t="n">
         <v>-1.0403</v>
@@ -4130,16 +4130,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-5.31</v>
+        <v>-5.6754</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.8983</v>
+        <v>-3.0977</v>
       </c>
       <c r="D81" t="n">
-        <v>-3.0414</v>
+        <v>-3.1489</v>
       </c>
       <c r="E81" t="n">
-        <v>-5.31</v>
+        <v>-5.6754</v>
       </c>
       <c r="F81" t="n">
         <v>-3.31</v>
@@ -21848,7 +21848,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D442" t="n">
@@ -21888,7 +21888,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D443" t="n">
@@ -21928,7 +21928,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D444" t="n">
@@ -21968,7 +21968,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D445" t="n">
@@ -22008,7 +22008,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D446" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -22083,7 +22083,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -22123,7 +22123,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -22163,7 +22163,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -22203,7 +22203,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -22248,7 +22248,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D452" t="n">
@@ -22288,7 +22288,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D453" t="n">
@@ -22328,7 +22328,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D454" t="n">
@@ -22368,7 +22368,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D455" t="n">
@@ -22408,7 +22408,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D456" t="n">
@@ -22443,7 +22443,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -22483,7 +22483,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -22523,7 +22523,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -22563,7 +22563,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -22603,7 +22603,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -22648,7 +22648,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D462" t="n">
@@ -22688,7 +22688,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D463" t="n">
@@ -22728,7 +22728,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D464" t="n">
@@ -22768,7 +22768,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D465" t="n">
@@ -22808,7 +22808,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D466" t="n">
@@ -22843,7 +22843,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -22883,7 +22883,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -22923,7 +22923,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -22963,7 +22963,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -23003,7 +23003,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -30248,7 +30248,7 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D652" t="n">
@@ -30288,7 +30288,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D653" t="n">
@@ -30328,7 +30328,7 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D654" t="n">
@@ -30368,7 +30368,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D655" t="n">
@@ -30408,7 +30408,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D656" t="n">
@@ -30443,7 +30443,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -30483,7 +30483,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -30523,7 +30523,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -30563,7 +30563,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -30603,7 +30603,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -30648,7 +30648,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D662" t="n">
@@ -30688,7 +30688,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D663" t="n">
@@ -30728,7 +30728,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D664" t="n">
@@ -30768,7 +30768,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D665" t="n">
@@ -30808,7 +30808,7 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="D666" t="n">
@@ -30843,7 +30843,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -30883,7 +30883,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -30923,7 +30923,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -30963,7 +30963,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -31003,7 +31003,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Rebels</t>
+          <t>RBLS</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
